--- a/Choke_Slam_export.xlsx
+++ b/Choke_Slam_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1241"/>
+  <dimension ref="A1:Q1252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84359,6 +84359,767 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>S08E01_Genesis</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Baltimore Arena</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>Rosemary vs. Megumi Kudo vs. Madusa</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr"/>
+      <c r="G1242" t="inlineStr"/>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>Rosemary, Megumi Kudo, Madusa</t>
+        </is>
+      </c>
+      <c r="I1242" t="inlineStr">
+        <is>
+          <t>Rosemary</t>
+        </is>
+      </c>
+      <c r="J1242" t="inlineStr">
+        <is>
+          <t>Megumi Kudo, Madusa</t>
+        </is>
+      </c>
+      <c r="K1242" t="inlineStr"/>
+      <c r="L1242" t="inlineStr">
+        <is>
+          <t>Rosemary won a triple threat match against Megumi Kudo &amp; Madusa in  16:09</t>
+        </is>
+      </c>
+      <c r="M1242" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="N1242" t="n">
+        <v>83</v>
+      </c>
+      <c r="O1242" t="inlineStr">
+        <is>
+          <t>★★★¾</t>
+        </is>
+      </c>
+      <c r="P1242" t="inlineStr"/>
+      <c r="Q1242" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>S08E01_Genesis</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Baltimore Arena</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>Satoshi Kojima vs. Randy Orton vs. The Miz</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr"/>
+      <c r="G1243" t="inlineStr"/>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>Satoshi Kojima, Randy Orton, The Miz</t>
+        </is>
+      </c>
+      <c r="I1243" t="inlineStr">
+        <is>
+          <t>Randy Orton</t>
+        </is>
+      </c>
+      <c r="J1243" t="inlineStr">
+        <is>
+          <t>Satoshi Kojima, The Miz</t>
+        </is>
+      </c>
+      <c r="K1243" t="inlineStr"/>
+      <c r="L1243" t="inlineStr">
+        <is>
+          <t>Randy Orton won a triple threat match against Satoshi Kojima &amp; The Miz in  23:48</t>
+        </is>
+      </c>
+      <c r="M1243" t="inlineStr">
+        <is>
+          <t>23:48</t>
+        </is>
+      </c>
+      <c r="N1243" t="n">
+        <v>100</v>
+      </c>
+      <c r="O1243" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="P1243" t="inlineStr"/>
+      <c r="Q1243" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>S08E01_Genesis</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Baltimore Arena</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>Steve Austin vs. SANADA vs. Yokozuna</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr"/>
+      <c r="G1244" t="inlineStr"/>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>Steve Austin, SANADA, Yokozuna</t>
+        </is>
+      </c>
+      <c r="I1244" t="inlineStr">
+        <is>
+          <t>Yokozuna</t>
+        </is>
+      </c>
+      <c r="J1244" t="inlineStr">
+        <is>
+          <t>Steve Austin, SANADA</t>
+        </is>
+      </c>
+      <c r="K1244" t="inlineStr"/>
+      <c r="L1244" t="inlineStr">
+        <is>
+          <t>Yokozuna won a triple threat match against Steve Austin &amp; SANADA in  31:19</t>
+        </is>
+      </c>
+      <c r="M1244" t="inlineStr">
+        <is>
+          <t>31:19</t>
+        </is>
+      </c>
+      <c r="N1244" t="n">
+        <v>94</v>
+      </c>
+      <c r="O1244" t="inlineStr">
+        <is>
+          <t>★★★★½</t>
+        </is>
+      </c>
+      <c r="P1244" t="inlineStr"/>
+      <c r="Q1244" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>S08E01_Genesis</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>Baltimore Arena</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>No DQ Tornado Tag Team: Militanter Mummenschanz vs. Sweet 'n Sour Elite</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>Tag Team, Tornado</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr"/>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>Masahiro Chono, Mick Foley, Cesaro, Satoshi Kojima</t>
+        </is>
+      </c>
+      <c r="I1245" t="inlineStr">
+        <is>
+          <t>Masahiro Chono, Mick Foley</t>
+        </is>
+      </c>
+      <c r="J1245" t="inlineStr">
+        <is>
+          <t>Cesaro, Satoshi Kojima</t>
+        </is>
+      </c>
+      <c r="K1245" t="inlineStr"/>
+      <c r="L1245" t="inlineStr">
+        <is>
+          <t>Masahiro Chono beat Cesaro in 11 Min 16 Sec with a STF</t>
+        </is>
+      </c>
+      <c r="M1245" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="N1245" t="n">
+        <v>75</v>
+      </c>
+      <c r="O1245" t="inlineStr">
+        <is>
+          <t>★★★¼</t>
+        </is>
+      </c>
+      <c r="P1245" t="inlineStr"/>
+      <c r="Q1245" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>S08E01_Genesis</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>Baltimore Arena</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>Best 2 out of 3 Falls: Sweet 'n Sour Elite vs. Saint Rebel Radicalz</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>2 out of 3 Falls</t>
+        </is>
+      </c>
+      <c r="G1246" t="inlineStr"/>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>Cesaro, Satoshi Kojima, Kazuchika Okada, The Miz</t>
+        </is>
+      </c>
+      <c r="I1246" t="inlineStr">
+        <is>
+          <t>Kazuchika Okada, The Miz</t>
+        </is>
+      </c>
+      <c r="J1246" t="inlineStr">
+        <is>
+          <t>Cesaro, Satoshi Kojima</t>
+        </is>
+      </c>
+      <c r="K1246" t="inlineStr"/>
+      <c r="L1246" t="inlineStr">
+        <is>
+          <t>The Miz beat Cesaro in 44 Min 26 Sec with a Sleeper Hold</t>
+        </is>
+      </c>
+      <c r="M1246" t="inlineStr">
+        <is>
+          <t>120:120</t>
+        </is>
+      </c>
+      <c r="N1246" t="n">
+        <v>97</v>
+      </c>
+      <c r="O1246" t="inlineStr">
+        <is>
+          <t>★★★★¾</t>
+        </is>
+      </c>
+      <c r="P1246" t="inlineStr"/>
+      <c r="Q1246" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>S08E01_Genesis</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Baltimore Arena</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>Lumberjack: Saint Rebel Radicalz vs. Militanter Mummenschanz</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr"/>
+      <c r="G1247" t="inlineStr"/>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>Kazuchika Okada, The Miz, Masahiro Chono, Mick Foley</t>
+        </is>
+      </c>
+      <c r="I1247" t="inlineStr">
+        <is>
+          <t>Kazuchika Okada, The Miz</t>
+        </is>
+      </c>
+      <c r="J1247" t="inlineStr">
+        <is>
+          <t>Masahiro Chono, Mick Foley</t>
+        </is>
+      </c>
+      <c r="K1247" t="inlineStr"/>
+      <c r="L1247" t="inlineStr">
+        <is>
+          <t>Kazuchika Okada beat Mankind in 50 Min 28 Sec with a Cobra Hold</t>
+        </is>
+      </c>
+      <c r="M1247" t="inlineStr">
+        <is>
+          <t>50:28</t>
+        </is>
+      </c>
+      <c r="N1247" t="n">
+        <v>93</v>
+      </c>
+      <c r="O1247" t="inlineStr">
+        <is>
+          <t>★★★★½</t>
+        </is>
+      </c>
+      <c r="P1247" t="inlineStr"/>
+      <c r="Q1247" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>S08E01_Genesis</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Baltimore Arena</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>Money in the Bank Match</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>Money in the Bank</t>
+        </is>
+      </c>
+      <c r="G1248" t="inlineStr"/>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>Chris Benoit, Mick Foley, Rosemary, Cesaro, Madusa, Kazuchika Okada</t>
+        </is>
+      </c>
+      <c r="I1248" t="inlineStr">
+        <is>
+          <t>Kazuchika Okada</t>
+        </is>
+      </c>
+      <c r="J1248" t="inlineStr">
+        <is>
+          <t>Chris Benoit, Mick Foley, Rosemary, Cesaro, Madusa</t>
+        </is>
+      </c>
+      <c r="K1248" t="inlineStr"/>
+      <c r="L1248" t="inlineStr">
+        <is>
+          <t>Kazuchika Okada won a six-pack scramble match against Chris Benoit, Mankind, Rosemary, Cesaro, &amp;Madusa in  20:18</t>
+        </is>
+      </c>
+      <c r="M1248" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="N1248" t="n">
+        <v>89</v>
+      </c>
+      <c r="O1248" t="inlineStr">
+        <is>
+          <t>★★★★¼</t>
+        </is>
+      </c>
+      <c r="P1248" t="inlineStr"/>
+      <c r="Q1248" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>S08E01_Genesis</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Baltimore Arena</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>Choke Slam International Championship: Chris Benoit vs. Matanza Cueto vs. Masahiro Chono vs. Hiroshi Tanahashi (c)</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr"/>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>Choke Slam International Championship</t>
+        </is>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>Chris Benoit, Matanza Cueto, Masahiro Chono, Hiroshi Tanahashi</t>
+        </is>
+      </c>
+      <c r="I1249" t="inlineStr">
+        <is>
+          <t>Masahiro Chono</t>
+        </is>
+      </c>
+      <c r="J1249" t="inlineStr">
+        <is>
+          <t>Chris Benoit, Matanza Cueto, Hiroshi Tanahashi</t>
+        </is>
+      </c>
+      <c r="K1249" t="inlineStr"/>
+      <c r="L1249" t="inlineStr">
+        <is>
+          <t>Masahiro Chono won a four-corners match against Chris Benoit, Matanza Cueto, &amp;Hiroshi Tanahashi in  18:18</t>
+        </is>
+      </c>
+      <c r="M1249" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="N1249" t="n">
+        <v>91</v>
+      </c>
+      <c r="O1249" t="inlineStr">
+        <is>
+          <t>★★★★¼</t>
+        </is>
+      </c>
+      <c r="P1249" t="inlineStr"/>
+      <c r="Q1249" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>S08E01_Genesis</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Baltimore Arena</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>Best 2 out of 3 Falls: Randy Orton vs. SANADA</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>2 out of 3 Falls</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr"/>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>Randy Orton, SANADA</t>
+        </is>
+      </c>
+      <c r="I1250" t="inlineStr">
+        <is>
+          <t>SANADA</t>
+        </is>
+      </c>
+      <c r="J1250" t="inlineStr">
+        <is>
+          <t>Randy Orton</t>
+        </is>
+      </c>
+      <c r="K1250" t="inlineStr"/>
+      <c r="L1250" t="inlineStr">
+        <is>
+          <t>SANADA beat Randy Orton in 13 Min 54 Sec with a Japanese Leg Roll Clutch</t>
+        </is>
+      </c>
+      <c r="M1250" t="inlineStr">
+        <is>
+          <t>31:31</t>
+        </is>
+      </c>
+      <c r="N1250" t="n">
+        <v>79</v>
+      </c>
+      <c r="O1250" t="inlineStr">
+        <is>
+          <t>★★★½</t>
+        </is>
+      </c>
+      <c r="P1250" t="inlineStr"/>
+      <c r="Q1250" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>S08E01_Genesis</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Baltimore Arena</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>Barbed Wire Deathmatch: Matanza Cueto vs. LePunisseur</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr"/>
+      <c r="G1251" t="inlineStr"/>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>Matanza Cueto, LePunisseur</t>
+        </is>
+      </c>
+      <c r="I1251" t="inlineStr">
+        <is>
+          <t>LePunisseur</t>
+        </is>
+      </c>
+      <c r="J1251" t="inlineStr">
+        <is>
+          <t>Matanza Cueto</t>
+        </is>
+      </c>
+      <c r="K1251" t="inlineStr"/>
+      <c r="L1251" t="inlineStr">
+        <is>
+          <t>LePunisseur beat Matanza Cueto in 12 Min 47 Sec with a Sleeper Hold</t>
+        </is>
+      </c>
+      <c r="M1251" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="N1251" t="n">
+        <v>87</v>
+      </c>
+      <c r="O1251" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="P1251" t="inlineStr"/>
+      <c r="Q1251" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>S08E01_Genesis</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Baltimore Arena</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>Falls Count Anywhere - Choke Slam World Championship: Yokozuna vs. Steve Austin (c)</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr"/>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>Choke Slam World Championship</t>
+        </is>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>Yokozuna, Steve Austin</t>
+        </is>
+      </c>
+      <c r="I1252" t="inlineStr">
+        <is>
+          <t>Yokozuna</t>
+        </is>
+      </c>
+      <c r="J1252" t="inlineStr">
+        <is>
+          <t>Steve Austin</t>
+        </is>
+      </c>
+      <c r="K1252" t="inlineStr"/>
+      <c r="L1252" t="inlineStr">
+        <is>
+          <t>Yokozuna beat Steve Austin in 13 Min 43 Sec with a BANZAI DROP</t>
+        </is>
+      </c>
+      <c r="M1252" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="N1252" t="n">
+        <v>96</v>
+      </c>
+      <c r="O1252" t="inlineStr">
+        <is>
+          <t>★★★★¾</t>
+        </is>
+      </c>
+      <c r="P1252" t="inlineStr"/>
+      <c r="Q1252" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
